--- a/docs/設計書/詳細設計書.xlsx
+++ b/docs/設計書/詳細設計書.xlsx
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'カラム定義'!$A$4:$I$321</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'テーブル制約'!$A$4:$C$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ビュー'!$A$4:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RPC'!$A$4:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RPC'!$A$4:$D$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'内部関数'!$A$4:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'失敗の分類'!$A$4:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'外部連携詳細'!$A$4:$B$13</definedName>
@@ -12716,7 +12716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13071,45 +13071,49 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
+    <row r="22" ht="49" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>public.record_instagram_connection</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>p_connection uuid, p_tenant uuid, p_member uuid, p_ig_user_id text, p_ig_username text, p_account_type text, p_token_ciphertext text, p_token_iv text, p_key_version smallint, p_expires_at timestamptz</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>前の連携の解除・新しい連携・最初のトークンを同じトランザクションで記録する。暗号文は API関数が AES-256-GCM で作る（ADR-0007）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>V8</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>public.try_consume_image_generation</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>p_tenant uuid, p_limit int</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>1回分を確保する。上限に達していたら allowed = false（同時に呼ばれても上限を超えない。NFR-005-03）</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>V8</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>public.try_consume_llm</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>p_tenant uuid, p_model text, p_limit int</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
@@ -13119,19 +13123,15 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>public.image_generation_usage_of</t>
+          <t>public.try_consume_llm</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>p_tenant uuid</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>今日の画像生成の回数（確保しない。事前確認と画面の残り回数に使う）</t>
-        </is>
-      </c>
+          <t>p_tenant uuid, p_model text, p_limit int</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -13141,13 +13141,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>public.image_generation_usage</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
+          <t>public.image_generation_usage_of</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>p_tenant uuid</t>
+        </is>
+      </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>画面用（ログイン中のメンバーの団体）</t>
+          <t>今日の画像生成の回数（確保しない。事前確認と画面の残り回数に使う）</t>
         </is>
       </c>
     </row>
@@ -13159,52 +13163,48 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>public.save_post_revision</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>p_post uuid, p_revision jsonb</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
+          <t>public.image_generation_usage</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>画面用（ログイン中のメンバーの団体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>V10</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>public.save_post_revision</t>
+          <t>public.record_image_generation</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>p_post uuid, p_revision jsonb</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>{role:'CLOSING'}]}</t>
-        </is>
-      </c>
+          <t>p_id uuid, p_tenant uuid, p_member uuid, p_style text, p_prompt_ja text, p_prompt_en text, p_provider text, p_model text, p_outcome text, p_candidate_count int</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>V10</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>public.approve_post</t>
+          <t>public.save_post_revision</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>p_post uuid, p_revision uuid, p_scheduled_at timestamptz</t>
+          <t>p_post uuid, p_revision jsonb</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr"/>
@@ -13217,59 +13217,55 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>public.save_post_revision</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>p_post uuid, p_revision jsonb</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>{role:'CLOSING'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>public.approve_post</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>p_post uuid, p_revision uuid, p_scheduled_at timestamptz</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
           <t>public.register_background_photo</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>p_storage_path text, p_description text</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>V10</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>public.retire_background_photo</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>p_id uuid</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>写真は消さず「使わない」にした出来事を追記する（既存の投稿の画像化には使える）。すでに使わないなら何もしない</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>V10</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>public.create_prompt_version</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>p_purpose text, p_body text</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>新しい版を作る（有効にはしない。activate_prompt_version で有効にする）</t>
-        </is>
-      </c>
+      <c r="D31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
@@ -13279,40 +13275,194 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
+          <t>public.retire_background_photo</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>p_id uuid</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>写真は消さず「使わない」にした出来事を追記する（既存の投稿の画像化には使える）。すでに使わないなら何もしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>public.save_post_style_settings</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>p_band_text text, p_cover_targets text[], p_closing_message text, p_account_introduction text, p_caption_footer text, p_fixed_hashtags text[], p_logo_storage_path text default null</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>新しい版を作る（版は変更しない）。戻り値は新しい版番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>public.create_prompt_version</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>p_purpose text, p_body text</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>新しい版を作る（有効にはしない。activate_prompt_version で有効にする）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>public.activate_prompt_version</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>p_id uuid</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>有効にする（同じ用途の前の有効な版は、有効化の履歴に残るだけで無効になる）。すでに有効なら何もしない</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>V10</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>public.record_idea</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>p_id uuid, p_tenant uuid, p_member uuid, p_body text</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>public.record_generation</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>p_id uuid, p_tenant uuid, p_member uuid, p_purpose text, p_route text, p_idea uuid, p_prompt_version uuid, p_input jsonb, p_outcome text, p_attempts jsonb, p_result jsonb, p_parent uuid, p_instruction text</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>p_parent・p_instruction: 修正指示のときだけ（両方を付けるか、両方 null）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>public.record_template_render</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>p_revision uuid, p_approval_event bigint, p_position int, p_storage_path text, p_width int, p_height int, p_byte_size int</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>画像化した JPEG の記録（承認の出来事ごと。保存先は {団体}/renders/{承認の出来事}/{順番}.jpg に限る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>public.record_template_publish_media</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>p_revision uuid, p_approval_event bigint, p_position int, p_storage_path text, p_width int, p_height int, p_byte_size int</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TEMPLATE の版の公開用 JPEG の記録（承認の出来事ごと。media-public の {団体}/{ファイル名}.jpg）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="49" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>public.record_generated_background</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>p_tenant uuid, p_member uuid, p_storage_path text, p_generation uuid, p_position int, p_description text</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>説明文: 改行・制御文字を拒否してから、前後の空白を取り除いて1〜100文字を検査し、取り除いた値を保存する（TS の BackgroundPhoto.violationsOfDescription と同じ）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D33"/>
+  <autoFilter ref="A4:D40"/>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
